--- a/CNPV_2018/Dataset_DPTO_CNPV2018.xlsx
+++ b/CNPV_2018/Dataset_DPTO_CNPV2018.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -425,6 +425,11 @@
           <t>ocupacion_dpto</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dpto_clean</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -471,6 +476,11 @@
       <c r="N2">
         <v>44</v>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ANTIOQUIA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -517,6 +527,11 @@
       <c r="N3">
         <v>38.71</v>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ATLANTICO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -563,6 +578,11 @@
       <c r="N4">
         <v>51.79</v>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>BOGOTA, D.C.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -609,6 +629,11 @@
       <c r="N5">
         <v>37.28</v>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>BOLIVAR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -655,6 +680,11 @@
       <c r="N6">
         <v>38.45</v>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>BOYACA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -701,6 +731,11 @@
       <c r="N7">
         <v>43.14</v>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>CALDAS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -747,6 +782,11 @@
       <c r="N8">
         <v>38.86</v>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>CAQUETA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -793,6 +833,11 @@
       <c r="N9">
         <v>37.83</v>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>CAUCA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -839,6 +884,11 @@
       <c r="N10">
         <v>36.88</v>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>CESAR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -885,6 +935,11 @@
       <c r="N11">
         <v>34.87</v>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>CORDOBA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -931,6 +986,11 @@
       <c r="N12">
         <v>48.22</v>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>CUNDINAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -977,6 +1037,11 @@
       <c r="N13">
         <v>31.67</v>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>CHOCO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -1023,6 +1088,11 @@
       <c r="N14">
         <v>40.4</v>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>HUILA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1069,6 +1139,11 @@
       <c r="N15">
         <v>29.2</v>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>LA GUAJIRA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1115,6 +1190,11 @@
       <c r="N16">
         <v>36.14</v>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>MAGDALENA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1161,6 +1241,11 @@
       <c r="N17">
         <v>42.64</v>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1207,6 +1292,11 @@
       <c r="N18">
         <v>39.01</v>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NARINO</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1253,6 +1343,11 @@
       <c r="N19">
         <v>41.34</v>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NORTE DE SANTANDER</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1299,6 +1394,11 @@
       <c r="N20">
         <v>40.96</v>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>QUINDIO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -1345,6 +1445,11 @@
       <c r="N21">
         <v>43.72</v>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>RISARALDA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1391,6 +1496,11 @@
       <c r="N22">
         <v>42.74</v>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>SANTANDER</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1437,6 +1547,11 @@
       <c r="N23">
         <v>34.16</v>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1483,6 +1598,11 @@
       <c r="N24">
         <v>40.41</v>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>TOLIMA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1529,6 +1649,11 @@
       <c r="N25">
         <v>43.25</v>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>VALLE DEL CAUCA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1575,6 +1700,11 @@
       <c r="N26">
         <v>38.03</v>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>ARAUCA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1621,6 +1751,11 @@
       <c r="N27">
         <v>39.52</v>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>CASANARE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1667,6 +1802,11 @@
       <c r="N28">
         <v>38.45</v>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>PUTUMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1713,6 +1853,11 @@
       <c r="N29">
         <v>57.86</v>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>ARCHIPIELAGO DE SAN ANDRES</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1759,6 +1904,11 @@
       <c r="N30">
         <v>33.36</v>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1805,6 +1955,11 @@
       <c r="N31">
         <v>25.41</v>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>GUAINIA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1851,6 +2006,11 @@
       <c r="N32">
         <v>42.22</v>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>GUAVIARE</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1897,6 +2057,11 @@
       <c r="N33">
         <v>13.71</v>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>VAUPES</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1942,6 +2107,11 @@
       </c>
       <c r="N34">
         <v>18.31</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>VICHADA</t>
+        </is>
       </c>
     </row>
   </sheetData>
